--- a/public/download/testimport 2.xlsx
+++ b/public/download/testimport 2.xlsx
@@ -28,7 +28,7 @@
     <t xml:space="preserve">product_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Website URL SS</t>
+    <t xml:space="preserve">website_url_ss</t>
   </si>
   <si>
     <t xml:space="preserve">description</t>
@@ -37,10 +37,10 @@
     <t xml:space="preserve">description_en</t>
   </si>
   <si>
-    <t xml:space="preserve">Workflow </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online Date</t>
+    <t xml:space="preserve">workflow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">online_date</t>
   </si>
   <si>
     <t xml:space="preserve">0305092001031</t>
@@ -389,6 +389,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="47.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="88.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.98"/>
